--- a/temp/MACRO_VISA_20241012.xlsx
+++ b/temp/MACRO_VISA_20241012.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Macro VISA</t>
+          <t>MACRO VISA</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20241012.xlsx
+++ b/temp/MACRO_VISA_20241012.xlsx
@@ -471,12 +471,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>-89004.8</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>-89004,8</t>
+        </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>
@@ -496,12 +498,14 @@
           <t>ARS</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>32990</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>32990,0</t>
+        </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MACRO VISA</t>
+          <t>Macro Visa</t>
         </is>
       </c>
     </row>

--- a/temp/MACRO_VISA_20241012.xlsx
+++ b/temp/MACRO_VISA_20241012.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>005302* ON FIT Cuota 05/06</t>
+          <t>ON FIT Cuota 05/06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
